--- a/patient_registration_form_templates/008_cardiology_discharge_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/008_cardiology_discharge_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -896,8 +896,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -925,12 +925,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'no_heavy_lifting_(&gt;10_lbs)',_'value':_'heavy_lifting'}</t>
+          <t>no_heavy_lifting_(&gt;10_lbs)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'No Heavy Lifting (&gt;10 lbs)', 'value': 'heavy_lifting'}</t>
+          <t>No Heavy Lifting (&gt;10 lbs)</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no_driving',_'value':_'driving'}</t>
+          <t>no_driving</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No Driving', 'value': 'driving'}</t>
+          <t>No Driving</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'strenuous_exercise'}</t>
+          <t>strenuous_exercise</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'strenuous_exercise'}</t>
+          <t>strenuous exercise</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'limited_stairs',_'value':_'limited_stairs'}</t>
+          <t>limited_stairs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Limited Stairs', 'value': 'limited_stairs'}</t>
+          <t>Limited Stairs</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'standard_cardiac_diet',_'value':_'cardiac_diet'}</t>
+          <t>standard_cardiac_diet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Cardiac Diet', 'value': 'cardiac_diet'}</t>
+          <t>Standard Cardiac Diet</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'low_sodium_(&lt;2000mg)',_'value':_'low_sodium'}</t>
+          <t>low_sodium_(&lt;2000mg)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Low Sodium (&lt;2000mg)', 'value': 'low_sodium'}</t>
+          <t>Low Sodium (&lt;2000mg)</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fluid_restricted',_'value':_'fluid_restricted'}</t>
+          <t>fluid_restricted</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fluid Restricted', 'value': 'fluid_restricted'}</t>
+          <t>Fluid Restricted</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'diabetic_friendly',_'value':_'diabetic'}</t>
+          <t>diabetic_friendly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetic Friendly', 'value': 'diabetic'}</t>
+          <t>Diabetic Friendly</t>
         </is>
       </c>
     </row>
